--- a/DIY_Alkalinity_Monitor_Price_Sheet.xlsx
+++ b/DIY_Alkalinity_Monitor_Price_Sheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
   <si>
     <t xml:space="preserve">DIY Ratiometric Alkalinity Monitor — Component Price Sheet</t>
   </si>
@@ -127,16 +127,10 @@
     <t xml:space="preserve">Must run both directions. Kamoer FX-STP or similar. Draws from and returns to reference reservoir.</t>
   </si>
   <si>
-    <t xml:space="preserve">Peristaltic dosing pump, 12V (Pump B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard direction only. Kamoer, Jebao, or BRS model. Draws from tank sump.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peristaltic/diaphragm drain pump, 12V (Pump C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higher flow preferred for fast drain. Empties chamber to waste.</t>
+    <t xml:space="preserve">Reversible peristaltic pump, 12V (Pump B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must run both directions, same as Pump A. Draws tank water in and returns it to the sump after measurement. Kamoer FX-STP or similar.</t>
   </si>
   <si>
     <t xml:space="preserve">Micro diaphragm air pump</t>
@@ -935,7 +929,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1257,7 +1251,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>9</v>
       </c>
@@ -1268,14 +1262,14 @@
         <v>36</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F18" s="12" t="n">
         <f aca="false">(D18+E18)/2</f>
-        <v>32.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1289,14 +1283,14 @@
         <v>38</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">(D19+E19)/2</f>
-        <v>27.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1310,463 +1304,452 @@
         <v>40</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">(D20+E20)/2</f>
-        <v>10</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">(D21+E21)/2</f>
-        <v>3.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">(D22+E22)/2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <f aca="false">(D24+E24)/2</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="12" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="8" t="n">
+      <c r="F25" s="12" t="n">
+        <f aca="false">(D25+E25)/2</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <f aca="false">(D26+E26)/2</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <f aca="false">(D27+E27)/2</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E28" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <f aca="false">(D23+E23)/2</f>
+      <c r="F28" s="8" t="n">
+        <f aca="false">(D28+E28)/2</f>
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" s="8" t="n">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <f aca="false">(D29+E29)/2</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <f aca="false">(D31+E31)/2</f>
         <v>30</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <f aca="false">(D25+E25)/2</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <f aca="false">(D26+E26)/2</f>
+    </row>
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <f aca="false">(D32+E32)/2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="17" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="8" t="n">
+      <c r="E33" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <f aca="false">(D33+E33)/2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="E27" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <f aca="false">(D27+E27)/2</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <f aca="false">(D28+E28)/2</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <f aca="false">(D29+E29)/2</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <f aca="false">(D30+E30)/2</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" s="17" t="n">
-        <f aca="false">(D32+E32)/2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <f aca="false">(D33+E33)/2</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="21" t="n">
         <f aca="false">(D34+E34)/2</f>
         <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="19" t="s">
+      <c r="A35" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="21" t="n">
+      <c r="D35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="F35" s="17" t="n">
         <f aca="false">(D35+E35)/2</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="15" t="s">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <f aca="false">(D36+E36)/2</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>76</v>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25" t="n">
+        <f aca="false">SUM(D5:D15)</f>
+        <v>167.5</v>
+      </c>
+      <c r="E38" s="25" t="n">
+        <f aca="false">SUM(E5:E15)</f>
+        <v>269</v>
+      </c>
+      <c r="F38" s="25" t="n">
+        <f aca="false">SUM(F5:F15)</f>
+        <v>218.25</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
       <c r="D39" s="25" t="n">
-        <f aca="false">SUM(D5:D15)</f>
-        <v>167.5</v>
+        <f aca="false">SUM(D17:D22)</f>
+        <v>94</v>
       </c>
       <c r="E39" s="25" t="n">
-        <f aca="false">SUM(E5:E15)</f>
-        <v>269</v>
+        <f aca="false">SUM(E17:E22)</f>
+        <v>159</v>
       </c>
       <c r="F39" s="25" t="n">
-        <f aca="false">SUM(F5:F15)</f>
-        <v>218.25</v>
+        <f aca="false">SUM(F17:F22)</f>
+        <v>126.5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="25" t="n">
-        <f aca="false">SUM(D17:D23)</f>
-        <v>104</v>
+        <f aca="false">SUM(D24:D29)</f>
+        <v>58</v>
       </c>
       <c r="E40" s="25" t="n">
-        <f aca="false">SUM(E17:E23)</f>
-        <v>174</v>
+        <f aca="false">SUM(E24:E29)</f>
+        <v>125</v>
       </c>
       <c r="F40" s="25" t="n">
-        <f aca="false">SUM(F17:F23)</f>
-        <v>139</v>
+        <f aca="false">SUM(F24:F29)</f>
+        <v>91.5</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27" t="n">
+        <f aca="false">SUM(D31:D35)</f>
+        <v>10</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <f aca="false">SUM(E31:E35)</f>
+        <v>155</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <f aca="false">SUM(F31:F35)</f>
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="25" t="n">
-        <f aca="false">SUM(D25:D30)</f>
-        <v>58</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <f aca="false">SUM(E25:E30)</f>
-        <v>125</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <f aca="false">SUM(F25:F30)</f>
-        <v>91.5</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="29" t="n">
+        <f aca="false">D38+D39+D40</f>
+        <v>319.5</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <f aca="false">E38+E39+E40</f>
+        <v>553</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <f aca="false">F38+F39+F40</f>
+        <v>436.25</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="27" t="n">
-        <f aca="false">SUM(D32:D36)</f>
-        <v>10</v>
-      </c>
-      <c r="E42" s="27" t="n">
-        <f aca="false">SUM(E32:E36)</f>
-        <v>155</v>
-      </c>
-      <c r="F42" s="27" t="n">
-        <f aca="false">SUM(F32:F36)</f>
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31" t="n">
+        <f aca="false">D42+D41</f>
+        <v>329.5</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <f aca="false">E42+E41</f>
+        <v>708</v>
+      </c>
+      <c r="F43" s="31" t="n">
+        <f aca="false">F42+F41</f>
+        <v>518.75</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="29" t="n">
-        <f aca="false">D39+D40+D41</f>
-        <v>329.5</v>
-      </c>
-      <c r="E43" s="29" t="n">
-        <f aca="false">E39+E40+E41</f>
-        <v>568</v>
-      </c>
-      <c r="F43" s="29" t="n">
-        <f aca="false">F39+F40+F41</f>
-        <v>448.75</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="31" t="n">
-        <f aca="false">D43+D42</f>
-        <v>339.5</v>
-      </c>
-      <c r="E44" s="31" t="n">
-        <f aca="false">E43+E42</f>
-        <v>723</v>
-      </c>
-      <c r="F44" s="31" t="n">
-        <f aca="false">F43+F42</f>
-        <v>531.25</v>
-      </c>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46" s="32"/>
       <c r="C46" s="32"/>
@@ -1775,34 +1758,24 @@
       <c r="F46" s="32"/>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
+      <c r="A47" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" s="33"/>
       <c r="C48" s="33"/>
       <c r="D48" s="33"/>
       <c r="E48" s="33"/>
       <c r="F48" s="33"/>
-    </row>
-    <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1810,19 +1783,19 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:F49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/DIY_Alkalinity_Monitor_Price_Sheet.xlsx
+++ b/DIY_Alkalinity_Monitor_Price_Sheet.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">DIY Ratiometric Alkalinity Monitor — Component Price Sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Telegraham Tested  •  Firmware v2.1.1  •  All prices approximate US retail</t>
+    <t xml:space="preserve">TelegrahamTested  •  Firmware v2.1.1  •  All prices approximate US retail</t>
   </si>
   <si>
     <t xml:space="preserve">Qty</t>
